--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Identification de micro-organismes multirésistants</t>
+    <t>Logical model - FR LM Identification de micro-organismes multirésistants</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Identification de micro-organismes multirésistants</t>
+    <t>Entrée Identification de micro-organismes multirésistants</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,37 +250,168 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.identifiant</t>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Métadonnées de base</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+</t>
+  </si>
+  <si>
+    <t>Patient/subject information</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.subject</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Identifiant de l’observation</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.code</t>
+    <t>Identifiant de l’entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.identifier</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x]</t>
+  </si>
+  <si>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.performer</t>
+  </si>
+  <si>
+    <t>Exécutant (performer)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
+</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.informant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.informant</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date/Heure de création par l'auteur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.date</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.source</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.langue</t>
+  </si>
+  <si>
+    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
+La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
+La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.langue</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.code</t>
+  </si>
+  <si>
     <t>Code de l’observation</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Description narrative de l’observation</t>
   </si>
   <si>
     <t>fr-lm-identification-de-micro-organismes-multiresistants.statut</t>
@@ -296,16 +427,6 @@
     <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
   </si>
   <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de l’observation</t>
-  </si>
-  <si>
     <t>fr-lm-identification-de-micro-organismes-multiresistants.valeur</t>
   </si>
   <si>
@@ -314,16 +435,6 @@
   </si>
   <si>
     <t>Description sous forme textuelle des micro-organismes identifiés</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.auteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-auteur
-</t>
-  </si>
-  <si>
-    <t>Auteur</t>
   </si>
 </sst>
 </file>
@@ -625,11 +736,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ9"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.23828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="54.23828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="74.62109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="74.62109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -638,7 +749,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="63.95703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -659,7 +770,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="54.23828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.44140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -960,7 +1071,7 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
@@ -977,10 +1088,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1003,13 +1114,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1060,7 +1171,7 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1077,10 +1188,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1088,10 +1199,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1103,13 +1214,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1160,13 +1271,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1177,10 +1288,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1188,10 +1299,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1203,13 +1314,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1239,7 +1350,7 @@
         <v>73</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="Z6" t="s" s="2">
         <v>73</v>
@@ -1260,13 +1371,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1277,10 +1388,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1288,10 +1399,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1303,13 +1414,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1360,13 +1471,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1377,10 +1488,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1388,10 +1499,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1403,13 +1514,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1460,13 +1571,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1477,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1491,7 +1602,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1503,13 +1614,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1560,18 +1671,918 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
+      <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -749,7 +753,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1714,13 +1718,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1771,7 +1775,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1788,10 +1792,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1814,13 +1818,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1871,7 +1875,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1888,10 +1892,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1914,13 +1918,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1971,7 +1975,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1988,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2014,13 +2018,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2071,7 +2075,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2088,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2114,13 +2118,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2171,7 +2175,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2188,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2214,13 +2218,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2271,7 +2275,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2288,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2314,13 +2318,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2371,7 +2375,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2388,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2414,13 +2418,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2450,7 +2454,7 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>73</v>
@@ -2471,7 +2475,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2488,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2514,13 +2518,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2571,7 +2575,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="147">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-identification-de-micro-organismes-multiresistants.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-identification-de-micro-organismes-multiresistants.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.source</t>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-identification-de-micro-organismes-multiresistants.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -416,19 +458,6 @@
   </si>
   <si>
     <t>Code de l’observation</t>
-  </si>
-  <si>
-    <t>fr-lm-identification-de-micro-organismes-multiresistants.statut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l’observation</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
   </si>
   <si>
     <t>fr-lm-identification-de-micro-organismes-multiresistants.valeur</t>
@@ -740,11 +769,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="74.62109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="74.62109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="81.33203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="81.33203125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -753,7 +782,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -768,7 +797,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1518,13 +1547,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1575,7 +1604,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1592,10 +1621,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1618,13 +1647,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1675,7 +1704,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1692,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1718,13 +1747,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1775,7 +1804,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1792,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1818,7 +1847,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -1918,13 +1947,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1975,7 +2004,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1992,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2006,7 +2035,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2018,13 +2047,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2075,13 +2104,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2092,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2106,7 +2135,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2118,13 +2147,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2175,13 +2204,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2192,10 +2221,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2206,7 +2235,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2218,13 +2247,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2275,13 +2304,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2292,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2303,7 +2332,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2318,13 +2347,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2375,10 +2404,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2457,7 +2486,7 @@
         <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2475,7 +2504,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2492,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2503,7 +2532,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2518,13 +2547,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2575,10 +2604,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2587,6 +2616,306 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-identification-de-micro-organismes-multiresistants.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
